--- a/Heating_Element_Cost/HeatingElementCostEstimate.xlsx
+++ b/Heating_Element_Cost/HeatingElementCostEstimate.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://gtvault-my.sharepoint.com/personal/lcalimlim3_gatech_edu/Documents/Documents/GitHub/ASE6002PEK/Heating_Element_Cost/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/07531a99d7244c5b/Documents/GitHub/ASE6002PEK/Heating_Element_Cost/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="210" documentId="8_{2AB1BE43-61F4-4C7B-8CB2-E9B8FC65C95C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{128C3DE4-E432-418A-985A-0932C310A482}"/>
+  <xr:revisionPtr revIDLastSave="348" documentId="8_{2AB1BE43-61F4-4C7B-8CB2-E9B8FC65C95C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3703C27B-3252-4CAA-8BE6-7DB0A0AEA35B}"/>
   <bookViews>
-    <workbookView xWindow="6345" yWindow="1125" windowWidth="21570" windowHeight="11295" xr2:uid="{CB1A8A0D-9D97-4379-8165-4BCA07248889}"/>
+    <workbookView xWindow="9105" yWindow="5325" windowWidth="38700" windowHeight="15345" xr2:uid="{CB1A8A0D-9D97-4379-8165-4BCA07248889}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -434,6 +434,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1040,7 +1044,7 @@
         <v>42</v>
       </c>
       <c r="C14" s="4">
-        <v>1501</v>
+        <v>1500</v>
       </c>
       <c r="E14" t="s">
         <v>56</v>
@@ -1055,7 +1059,7 @@
       </c>
       <c r="C15">
         <f>(C12)^2/C14</f>
-        <v>8.2085276482345093E-2</v>
+        <v>8.2139999999999991E-2</v>
       </c>
       <c r="D15" t="s">
         <v>55</v>
@@ -1081,7 +1085,7 @@
       </c>
       <c r="C17">
         <f>((C11*C16))/C15</f>
-        <v>3.5424814639266288E-6</v>
+        <v>3.5401213830046256E-6</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -1093,7 +1097,7 @@
       </c>
       <c r="C18">
         <f>C17*C11</f>
-        <v>9.9048316646089584E-7</v>
+        <v>9.8982328427138153E-7</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -1105,7 +1109,7 @@
       </c>
       <c r="C19">
         <f>C18*8400</f>
-        <v>8.3200585982715243E-3</v>
+        <v>8.3145155878796041E-3</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -1117,7 +1121,7 @@
       </c>
       <c r="C20">
         <f>C19*C5</f>
-        <v>0.24960175794814574</v>
+        <v>0.24943546763638813</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -1264,7 +1268,7 @@
       </c>
       <c r="C37">
         <f>C34+C33+C30+C28+C20</f>
-        <v>8.899469490044396</v>
+        <v>8.8993031997326391</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
@@ -1276,7 +1280,7 @@
       </c>
       <c r="C38" s="13">
         <f>C20/C37</f>
-        <v>2.8046813153005209E-2</v>
+        <v>2.8028651461597789E-2</v>
       </c>
     </row>
   </sheetData>

--- a/Heating_Element_Cost/HeatingElementCostEstimate.xlsx
+++ b/Heating_Element_Cost/HeatingElementCostEstimate.xlsx
@@ -1,20 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://gtvault-my.sharepoint.com/personal/lcalimlim3_gatech_edu/Documents/Documents/GitHub/ASE6002PEK/Heating_Element_Cost/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="210" documentId="8_{2AB1BE43-61F4-4C7B-8CB2-E9B8FC65C95C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{128C3DE4-E432-418A-985A-0932C310A482}"/>
+  <xr:revisionPtr revIDLastSave="230" documentId="8_{2AB1BE43-61F4-4C7B-8CB2-E9B8FC65C95C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{27DE82D0-63FE-493A-864E-39B91B3EAE83}"/>
   <bookViews>
-    <workbookView xWindow="6345" yWindow="1125" windowWidth="21570" windowHeight="11295" xr2:uid="{CB1A8A0D-9D97-4379-8165-4BCA07248889}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{CB1A8A0D-9D97-4379-8165-4BCA07248889}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="UNC_Heat_Elem_Tol">Sheet1!$C$42</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -434,6 +437,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1040,7 +1047,7 @@
         <v>42</v>
       </c>
       <c r="C14" s="4">
-        <v>1501</v>
+        <v>1576.05</v>
       </c>
       <c r="E14" t="s">
         <v>56</v>
@@ -1055,7 +1062,7 @@
       </c>
       <c r="C15">
         <f>(C12)^2/C14</f>
-        <v>8.2085276482345093E-2</v>
+        <v>7.8176453792709627E-2</v>
       </c>
       <c r="D15" t="s">
         <v>55</v>
@@ -1081,7 +1088,7 @@
       </c>
       <c r="C17">
         <f>((C11*C16))/C15</f>
-        <v>3.5424814639266288E-6</v>
+        <v>3.7196055371229595E-6</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -1093,7 +1100,7 @@
       </c>
       <c r="C18">
         <f>C17*C11</f>
-        <v>9.9048316646089584E-7</v>
+        <v>1.0400073247839403E-6</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -1105,7 +1112,7 @@
       </c>
       <c r="C19">
         <f>C18*8400</f>
-        <v>8.3200585982715243E-3</v>
+        <v>8.7360615281850979E-3</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -1117,7 +1124,7 @@
       </c>
       <c r="C20">
         <f>C19*C5</f>
-        <v>0.24960175794814574</v>
+        <v>0.26208184584555294</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -1264,7 +1271,7 @@
       </c>
       <c r="C37">
         <f>C34+C33+C30+C28+C20</f>
-        <v>8.899469490044396</v>
+        <v>8.9119495779418045</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
@@ -1276,7 +1283,7 @@
       </c>
       <c r="C38" s="13">
         <f>C20/C37</f>
-        <v>2.8046813153005209E-2</v>
+        <v>2.9407913897340539E-2</v>
       </c>
     </row>
   </sheetData>

--- a/Heating_Element_Cost/HeatingElementCostEstimate.xlsx
+++ b/Heating_Element_Cost/HeatingElementCostEstimate.xlsx
@@ -1,21 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://gtvault-my.sharepoint.com/personal/lcalimlim3_gatech_edu/Documents/Documents/GitHub/ASE6002PEK/Heating_Element_Cost/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="230" documentId="8_{2AB1BE43-61F4-4C7B-8CB2-E9B8FC65C95C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{27DE82D0-63FE-493A-864E-39B91B3EAE83}"/>
+  <xr:revisionPtr revIDLastSave="237" documentId="8_{2AB1BE43-61F4-4C7B-8CB2-E9B8FC65C95C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CF8BDA18-BD47-4F36-AED1-3F8A1D299DCB}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{CB1A8A0D-9D97-4379-8165-4BCA07248889}"/>
+    <workbookView xWindow="6255" yWindow="420" windowWidth="21570" windowHeight="11295" xr2:uid="{CB1A8A0D-9D97-4379-8165-4BCA07248889}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
+    <definedName name="UNC_Heat_Elem_Cost">Sheet1!$B$40</definedName>
     <definedName name="UNC_Heat_Elem_Tol">Sheet1!$C$42</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="73">
   <si>
     <t xml:space="preserve">Cost estimation for heating element </t>
   </si>
@@ -252,6 +253,12 @@
   </si>
   <si>
     <t>Percentage of cost for coil</t>
+  </si>
+  <si>
+    <t>UNC_Heat_Elem_Cost</t>
+  </si>
+  <si>
+    <t>%variation</t>
   </si>
 </sst>
 </file>
@@ -760,7 +767,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A474961C-9B26-4F8E-9E1E-C6F56EBB70C1}">
-  <dimension ref="A1:J38"/>
+  <dimension ref="A1:J40"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="25.28515625" customWidth="1"/>
@@ -1270,7 +1277,7 @@
         <v>34</v>
       </c>
       <c r="C37">
-        <f>C34+C33+C30+C28+C20</f>
+        <f>(C34+C33+C30+C28+C20)*B40</f>
         <v>8.9119495779418045</v>
       </c>
     </row>
@@ -1284,6 +1291,17 @@
       <c r="C38" s="13">
         <f>C20/C37</f>
         <v>2.9407913897340539E-2</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>71</v>
+      </c>
+      <c r="B40">
+        <v>1</v>
+      </c>
+      <c r="C40" t="s">
+        <v>72</v>
       </c>
     </row>
   </sheetData>

--- a/Heating_Element_Cost/HeatingElementCostEstimate.xlsx
+++ b/Heating_Element_Cost/HeatingElementCostEstimate.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://gtvault-my.sharepoint.com/personal/lcalimlim3_gatech_edu/Documents/Documents/GitHub/ASE6002PEK/Heating_Element_Cost/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/07531a99d7244c5b/Documents/GitHub/ASE6002PEK/Heating_Element_Cost/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="237" documentId="8_{2AB1BE43-61F4-4C7B-8CB2-E9B8FC65C95C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CF8BDA18-BD47-4F36-AED1-3F8A1D299DCB}"/>
+  <xr:revisionPtr revIDLastSave="12504" documentId="121_{FDD03786-44D7-4CA4-9996-7C471CC56118}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0D1778C8-15E2-4A02-85A3-DA06A7A255DF}"/>
   <bookViews>
-    <workbookView xWindow="6255" yWindow="420" windowWidth="21570" windowHeight="11295" xr2:uid="{CB1A8A0D-9D97-4379-8165-4BCA07248889}"/>
+    <workbookView xWindow="9105" yWindow="5325" windowWidth="38700" windowHeight="15345" xr2:uid="{CB1A8A0D-9D97-4379-8165-4BCA07248889}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1054,7 +1054,7 @@
         <v>42</v>
       </c>
       <c r="C14" s="4">
-        <v>1576.05</v>
+        <v>1556.3679914586601</v>
       </c>
       <c r="E14" t="s">
         <v>56</v>
@@ -1069,7 +1069,7 @@
       </c>
       <c r="C15">
         <f>(C12)^2/C14</f>
-        <v>7.8176453792709627E-2</v>
+        <v>7.9165082214602125E-2</v>
       </c>
       <c r="D15" t="s">
         <v>55</v>
@@ -1095,7 +1095,7 @@
       </c>
       <c r="C17">
         <f>((C11*C16))/C15</f>
-        <v>3.7196055371229595E-6</v>
+        <v>3.6731544042578415E-6</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="C18">
         <f>C17*C11</f>
-        <v>1.0400073247839403E-6</v>
+        <v>1.0270195178936427E-6</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -1119,7 +1119,7 @@
       </c>
       <c r="C19">
         <f>C18*8400</f>
-        <v>8.7360615281850979E-3</v>
+        <v>8.6269639503065987E-3</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -1131,7 +1131,7 @@
       </c>
       <c r="C20">
         <f>C19*C5</f>
-        <v>0.26208184584555294</v>
+        <v>0.25880891850919796</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -1278,7 +1278,7 @@
       </c>
       <c r="C37">
         <f>(C34+C33+C30+C28+C20)*B40</f>
-        <v>8.9119495779418045</v>
+        <v>9.0699028722733015</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
@@ -1290,7 +1290,7 @@
       </c>
       <c r="C38" s="13">
         <f>C20/C37</f>
-        <v>2.9407913897340539E-2</v>
+        <v>2.8534916211768593E-2</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
@@ -1298,7 +1298,7 @@
         <v>71</v>
       </c>
       <c r="B40">
-        <v>1</v>
+        <v>1.0180976623118201</v>
       </c>
       <c r="C40" t="s">
         <v>72</v>

--- a/Heating_Element_Cost/HeatingElementCostEstimate.xlsx
+++ b/Heating_Element_Cost/HeatingElementCostEstimate.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/07531a99d7244c5b/Documents/GitHub/ASE6002PEK/Heating_Element_Cost/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="12504" documentId="121_{FDD03786-44D7-4CA4-9996-7C471CC56118}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0D1778C8-15E2-4A02-85A3-DA06A7A255DF}"/>
+  <xr:revisionPtr revIDLastSave="14044" documentId="121_{FDD03786-44D7-4CA4-9996-7C471CC56118}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3FEED952-0D2C-4CCD-A5B8-072D0A54688E}"/>
   <bookViews>
     <workbookView xWindow="9105" yWindow="5325" windowWidth="38700" windowHeight="15345" xr2:uid="{CB1A8A0D-9D97-4379-8165-4BCA07248889}"/>
   </bookViews>
@@ -1054,7 +1054,7 @@
         <v>42</v>
       </c>
       <c r="C14" s="4">
-        <v>1556.3679914586601</v>
+        <v>1412.3931741036199</v>
       </c>
       <c r="E14" t="s">
         <v>56</v>
@@ -1069,7 +1069,7 @@
       </c>
       <c r="C15">
         <f>(C12)^2/C14</f>
-        <v>7.9165082214602125E-2</v>
+        <v>8.7234916069454688E-2</v>
       </c>
       <c r="D15" t="s">
         <v>55</v>
@@ -1095,7 +1095,7 @@
       </c>
       <c r="C17">
         <f>((C11*C16))/C15</f>
-        <v>3.6731544042578415E-6</v>
+        <v>3.3333621845693334E-6</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="C18">
         <f>C17*C11</f>
-        <v>1.0270195178936427E-6</v>
+        <v>9.3201310018248416E-7</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -1119,7 +1119,7 @@
       </c>
       <c r="C19">
         <f>C18*8400</f>
-        <v>8.6269639503065987E-3</v>
+        <v>7.8289100415328671E-3</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -1131,7 +1131,7 @@
       </c>
       <c r="C20">
         <f>C19*C5</f>
-        <v>0.25880891850919796</v>
+        <v>0.23486730124598601</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -1278,7 +1278,7 @@
       </c>
       <c r="C37">
         <f>(C34+C33+C30+C28+C20)*B40</f>
-        <v>9.0699028722733015</v>
+        <v>8.5098240887779237</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
@@ -1290,7 +1290,7 @@
       </c>
       <c r="C38" s="13">
         <f>C20/C37</f>
-        <v>2.8534916211768593E-2</v>
+        <v>2.7599548333285789E-2</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
@@ -1298,7 +1298,7 @@
         <v>71</v>
       </c>
       <c r="B40">
-        <v>1.0180976623118201</v>
+        <v>0.957802799615592</v>
       </c>
       <c r="C40" t="s">
         <v>72</v>

--- a/Heating_Element_Cost/HeatingElementCostEstimate.xlsx
+++ b/Heating_Element_Cost/HeatingElementCostEstimate.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/07531a99d7244c5b/Documents/GitHub/ASE6002PEK/Heating_Element_Cost/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="14044" documentId="121_{FDD03786-44D7-4CA4-9996-7C471CC56118}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3FEED952-0D2C-4CCD-A5B8-072D0A54688E}"/>
+  <xr:revisionPtr revIDLastSave="14104" documentId="121_{FDD03786-44D7-4CA4-9996-7C471CC56118}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B5B0099A-AF2D-4D88-BA66-75015F18343D}"/>
   <bookViews>
     <workbookView xWindow="9105" yWindow="5325" windowWidth="38700" windowHeight="15345" xr2:uid="{CB1A8A0D-9D97-4379-8165-4BCA07248889}"/>
   </bookViews>
@@ -1054,7 +1054,7 @@
         <v>42</v>
       </c>
       <c r="C14" s="4">
-        <v>1412.3931741036199</v>
+        <v>22.5</v>
       </c>
       <c r="E14" t="s">
         <v>56</v>
@@ -1069,7 +1069,7 @@
       </c>
       <c r="C15">
         <f>(C12)^2/C14</f>
-        <v>8.7234916069454688E-2</v>
+        <v>5.476</v>
       </c>
       <c r="D15" t="s">
         <v>55</v>
@@ -1095,7 +1095,7 @@
       </c>
       <c r="C17">
         <f>((C11*C16))/C15</f>
-        <v>3.3333621845693334E-6</v>
+        <v>5.3101820745069381E-8</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="C18">
         <f>C17*C11</f>
-        <v>9.3201310018248416E-7</v>
+        <v>1.4847349264070721E-8</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -1119,7 +1119,7 @@
       </c>
       <c r="C19">
         <f>C18*8400</f>
-        <v>7.8289100415328671E-3</v>
+        <v>1.2471773381819405E-4</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -1131,7 +1131,7 @@
       </c>
       <c r="C20">
         <f>C19*C5</f>
-        <v>0.23486730124598601</v>
+        <v>3.7415320145458217E-3</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -1278,7 +1278,7 @@
       </c>
       <c r="C37">
         <f>(C34+C33+C30+C28+C20)*B40</f>
-        <v>8.5098240887779237</v>
+        <v>6.4783013502179738</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
@@ -1290,7 +1290,7 @@
       </c>
       <c r="C38" s="13">
         <f>C20/C37</f>
-        <v>2.7599548333285789E-2</v>
+        <v>5.7754831278726039E-4</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
@@ -1298,7 +1298,7 @@
         <v>71</v>
       </c>
       <c r="B40">
-        <v>0.957802799615592</v>
+        <v>0.74862420436354804</v>
       </c>
       <c r="C40" t="s">
         <v>72</v>

--- a/Heating_Element_Cost/HeatingElementCostEstimate.xlsx
+++ b/Heating_Element_Cost/HeatingElementCostEstimate.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/07531a99d7244c5b/Documents/GitHub/ASE6002PEK/Heating_Element_Cost/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="14104" documentId="121_{FDD03786-44D7-4CA4-9996-7C471CC56118}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B5B0099A-AF2D-4D88-BA66-75015F18343D}"/>
+  <xr:revisionPtr revIDLastSave="14750" documentId="121_{FDD03786-44D7-4CA4-9996-7C471CC56118}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{703A9BAF-F638-4089-B06D-0AA29CD739FE}"/>
   <bookViews>
     <workbookView xWindow="9105" yWindow="5325" windowWidth="38700" windowHeight="15345" xr2:uid="{CB1A8A0D-9D97-4379-8165-4BCA07248889}"/>
   </bookViews>
@@ -1278,7 +1278,7 @@
       </c>
       <c r="C37">
         <f>(C34+C33+C30+C28+C20)*B40</f>
-        <v>6.4783013502179738</v>
+        <v>8.4372690325080271</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
@@ -1290,7 +1290,7 @@
       </c>
       <c r="C38" s="13">
         <f>C20/C37</f>
-        <v>5.7754831278726039E-4</v>
+        <v>4.4345297040192038E-4</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
@@ -1298,7 +1298,7 @@
         <v>71</v>
       </c>
       <c r="B40">
-        <v>0.74862420436354804</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="C40" t="s">
         <v>72</v>

--- a/Heating_Element_Cost/HeatingElementCostEstimate.xlsx
+++ b/Heating_Element_Cost/HeatingElementCostEstimate.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/07531a99d7244c5b/Documents/GitHub/ASE6002PEK/Heating_Element_Cost/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="14750" documentId="121_{FDD03786-44D7-4CA4-9996-7C471CC56118}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{703A9BAF-F638-4089-B06D-0AA29CD739FE}"/>
+  <xr:revisionPtr revIDLastSave="16750" documentId="121_{FDD03786-44D7-4CA4-9996-7C471CC56118}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0153BC76-7ADF-4A3A-83F7-8B5AD2289B11}"/>
   <bookViews>
     <workbookView xWindow="9105" yWindow="5325" windowWidth="38700" windowHeight="15345" xr2:uid="{CB1A8A0D-9D97-4379-8165-4BCA07248889}"/>
   </bookViews>
@@ -1054,7 +1054,7 @@
         <v>42</v>
       </c>
       <c r="C14" s="4">
-        <v>22.5</v>
+        <v>1477.5</v>
       </c>
       <c r="E14" t="s">
         <v>56</v>
@@ -1069,7 +1069,7 @@
       </c>
       <c r="C15">
         <f>(C12)^2/C14</f>
-        <v>5.476</v>
+        <v>8.3390862944162439E-2</v>
       </c>
       <c r="D15" t="s">
         <v>55</v>
@@ -1095,7 +1095,7 @@
       </c>
       <c r="C17">
         <f>((C11*C16))/C15</f>
-        <v>5.3101820745069381E-8</v>
+        <v>3.4870195622595557E-6</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="C18">
         <f>C17*C11</f>
-        <v>1.4847349264070721E-8</v>
+        <v>9.7497593500731057E-7</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -1119,7 +1119,7 @@
       </c>
       <c r="C19">
         <f>C18*8400</f>
-        <v>1.2471773381819405E-4</v>
+        <v>8.1897978540614088E-3</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -1131,7 +1131,7 @@
       </c>
       <c r="C20">
         <f>C19*C5</f>
-        <v>3.7415320145458217E-3</v>
+        <v>0.24569393562184227</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -1278,7 +1278,7 @@
       </c>
       <c r="C37">
         <f>(C34+C33+C30+C28+C20)*B40</f>
-        <v>8.4372690325080271</v>
+        <v>3.656888932040427</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
@@ -1290,7 +1290,7 @@
       </c>
       <c r="C38" s="13">
         <f>C20/C37</f>
-        <v>4.4345297040192038E-4</v>
+        <v>6.718660046498949E-2</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
@@ -1298,7 +1298,7 @@
         <v>71</v>
       </c>
       <c r="B40">
-        <v>0.97499999999999998</v>
+        <v>0.41109140362786101</v>
       </c>
       <c r="C40" t="s">
         <v>72</v>
